--- a/results/nhanes__age-group__routine-blood-tests/results.xlsx
+++ b/results/nhanes__age-group__routine-blood-tests/results.xlsx
@@ -24,15 +24,15 @@
     <sheet name="select" sheetId="15" r:id="rId15"/>
     <sheet name="select_picks_summary" sheetId="16" r:id="rId16"/>
     <sheet name="pareto" sheetId="17" r:id="rId17"/>
-    <sheet name="external" sheetId="18" r:id="rId18"/>
-    <sheet name="shap_by_group" sheetId="19" r:id="rId19"/>
+    <sheet name="shap_by_group" sheetId="18" r:id="rId18"/>
+    <sheet name="lime_shap_agreement" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="388">
   <si>
     <t>Value</t>
   </si>
@@ -613,12 +613,18 @@
     <t>Reweighing (pre-processing)</t>
   </si>
   <si>
+    <t>Group-balanced SMOTE (pre-processing)</t>
+  </si>
+  <si>
     <t>Exponentiated Gradient (in-processing)</t>
   </si>
   <si>
     <t>Threshold Optimizer (post-processing)</t>
   </si>
   <si>
+    <t>Reject Option Classification (post-processing)</t>
+  </si>
+  <si>
     <t>Reweighing + Threshold Optimizer (hybrid)</t>
   </si>
   <si>
@@ -628,12 +634,18 @@
     <t>0.720 ± 0.002</t>
   </si>
   <si>
+    <t>0.716 ± 0.003</t>
+  </si>
+  <si>
     <t>0.691 ± 0.004</t>
   </si>
   <si>
     <t>0.697 ± 0.022</t>
   </si>
   <si>
+    <t>0.716 ± 0.004</t>
+  </si>
+  <si>
     <t>0.729 ± 0.013</t>
   </si>
   <si>
@@ -643,12 +655,18 @@
     <t>0.747 ± 0.005</t>
   </si>
   <si>
+    <t>0.833 ± 0.001</t>
+  </si>
+  <si>
     <t>0.783 ± 0.003</t>
   </si>
   <si>
     <t>0.697 ± 0.025</t>
   </si>
   <si>
+    <t>0.734 ± 0.008</t>
+  </si>
+  <si>
     <t>0.684 ± 0.020</t>
   </si>
   <si>
@@ -658,12 +676,18 @@
     <t>0.695 ± 0.003</t>
   </si>
   <si>
+    <t>0.687 ± 0.004</t>
+  </si>
+  <si>
     <t>0.658 ± 0.003</t>
   </si>
   <si>
     <t>0.642 ± 0.007</t>
   </si>
   <si>
+    <t>0.707 ± 0.004</t>
+  </si>
+  <si>
     <t>0.644 ± 0.003</t>
   </si>
   <si>
@@ -673,12 +697,18 @@
     <t>0.693 ± 0.007</t>
   </si>
   <si>
+    <t>0.678 ± 0.002</t>
+  </si>
+  <si>
     <t>0.698 ± 0.004</t>
   </si>
   <si>
     <t>0.644 ± 0.005</t>
   </si>
   <si>
+    <t>0.709 ± 0.007</t>
+  </si>
+  <si>
     <t>0.636 ± 0.005</t>
   </si>
   <si>
@@ -688,12 +718,18 @@
     <t>0.656 ± 0.005</t>
   </si>
   <si>
+    <t>0.643 ± 0.006</t>
+  </si>
+  <si>
     <t>0.605 ± 0.003</t>
   </si>
   <si>
     <t>0.554 ± 0.023</t>
   </si>
   <si>
+    <t>0.692 ± 0.005</t>
+  </si>
+  <si>
     <t>0.510 ± 0.018</t>
   </si>
   <si>
@@ -703,12 +739,18 @@
     <t>0.606 ± 0.010</t>
   </si>
   <si>
+    <t>0.431 ± 0.004</t>
+  </si>
+  <si>
     <t>0.562 ± 0.011</t>
   </si>
   <si>
     <t>0.559 ± 0.030</t>
   </si>
   <si>
+    <t>0.670 ± 0.009</t>
+  </si>
+  <si>
     <t>0.560 ± 0.027</t>
   </si>
   <si>
@@ -718,12 +760,18 @@
     <t>0.465 ± 0.003</t>
   </si>
   <si>
+    <t>0.456 ± 0.004</t>
+  </si>
+  <si>
     <t>0.421 ± 0.003</t>
   </si>
   <si>
     <t>0.405 ± 0.011</t>
   </si>
   <si>
+    <t>0.475 ± 0.005</t>
+  </si>
+  <si>
     <t>0.411 ± 0.004</t>
   </si>
   <si>
@@ -733,12 +781,18 @@
     <t>0.470 ± 0.009</t>
   </si>
   <si>
+    <t>0.489 ± 0.004</t>
+  </si>
+  <si>
     <t>0.490 ± 0.005</t>
   </si>
   <si>
     <t>0.406 ± 0.007</t>
   </si>
   <si>
+    <t>0.483 ± 0.009</t>
+  </si>
+  <si>
     <t>0.397 ± 0.006</t>
   </si>
   <si>
@@ -748,12 +802,18 @@
     <t>0.246 ± 0.006</t>
   </si>
   <si>
+    <t>0.218 ± 0.005</t>
+  </si>
+  <si>
     <t>0.093 ± 0.015</t>
   </si>
   <si>
     <t>0.077 ± 0.008</t>
   </si>
   <si>
+    <t>0.286 ± 0.017</t>
+  </si>
+  <si>
     <t>0.074 ± 0.008</t>
   </si>
   <si>
@@ -763,9 +823,15 @@
     <t>0.179 ± 0.009</t>
   </si>
   <si>
+    <t>0.195 ± 0.003</t>
+  </si>
+  <si>
     <t>0.212 ± 0.010</t>
   </si>
   <si>
+    <t>0.239 ± 0.026</t>
+  </si>
+  <si>
     <t>0.059 ± 0.006</t>
   </si>
   <si>
@@ -775,12 +841,18 @@
     <t>0.502 ± 0.009</t>
   </si>
   <si>
+    <t>0.543 ± 0.009</t>
+  </si>
+  <si>
     <t>0.773 ± 0.034</t>
   </si>
   <si>
     <t>0.793 ± 0.019</t>
   </si>
   <si>
+    <t>0.468 ± 0.025</t>
+  </si>
+  <si>
     <t>0.769 ± 0.028</t>
   </si>
   <si>
@@ -790,12 +862,18 @@
     <t>0.560 ± 0.016</t>
   </si>
   <si>
+    <t>0.266 ± 0.007</t>
+  </si>
+  <si>
     <t>0.436 ± 0.022</t>
   </si>
   <si>
     <t>0.801 ± 0.021</t>
   </si>
   <si>
+    <t>0.504 ± 0.044</t>
+  </si>
+  <si>
     <t>0.843 ± 0.016</t>
   </si>
   <si>
@@ -805,12 +883,18 @@
     <t>0.223 ± 0.015</t>
   </si>
   <si>
+    <t>0.227 ± 0.008</t>
+  </si>
+  <si>
     <t>0.077 ± 0.016</t>
   </si>
   <si>
     <t>0.027 ± 0.016</t>
   </si>
   <si>
+    <t>0.293 ± 0.016</t>
+  </si>
+  <si>
     <t>0.014 ± 0.015</t>
   </si>
   <si>
@@ -820,12 +904,18 @@
     <t>0.226 ± 0.025</t>
   </si>
   <si>
+    <t>0.276 ± 0.008</t>
+  </si>
+  <si>
     <t>0.265 ± 0.027</t>
   </si>
   <si>
     <t>0.034 ± 0.029</t>
   </si>
   <si>
+    <t>0.263 ± 0.028</t>
+  </si>
+  <si>
     <t>0.024 ± 0.017</t>
   </si>
   <si>
@@ -847,12 +937,18 @@
     <t>0.308 ± 0.005</t>
   </si>
   <si>
+    <t>0.333 ± 0.002</t>
+  </si>
+  <si>
     <t>0.361 ± 0.011</t>
   </si>
   <si>
     <t>0.345 ± 0.026</t>
   </si>
   <si>
+    <t>0.312 ± 0.008</t>
+  </si>
+  <si>
     <t>0.351 ± 0.017</t>
   </si>
   <si>
@@ -862,12 +958,18 @@
     <t>0.380 ± 0.007</t>
   </si>
   <si>
+    <t>0.337 ± 0.005</t>
+  </si>
+  <si>
     <t>0.366 ± 0.007</t>
   </si>
   <si>
     <t>0.353 ± 0.023</t>
   </si>
   <si>
+    <t>0.341 ± 0.014</t>
+  </si>
+  <si>
     <t>0.348 ± 0.016</t>
   </si>
   <si>
@@ -877,12 +979,18 @@
     <t>0.090 ± 0.003</t>
   </si>
   <si>
+    <t>0.067 ± 0.003</t>
+  </si>
+  <si>
     <t>0.014 ± 0.013</t>
   </si>
   <si>
     <t>0.040 ± 0.009</t>
   </si>
   <si>
+    <t>0.088 ± 0.012</t>
+  </si>
+  <si>
     <t>0.065 ± 0.016</t>
   </si>
   <si>
@@ -892,12 +1000,18 @@
     <t>0.046 ± 0.005</t>
   </si>
   <si>
+    <t>0.130 ± 0.001</t>
+  </si>
+  <si>
     <t>0.086 ± 0.007</t>
   </si>
   <si>
     <t>0.033 ± 0.010</t>
   </si>
   <si>
+    <t>0.062 ± 0.017</t>
+  </si>
+  <si>
     <t>0.023 ± 0.016</t>
   </si>
   <si>
@@ -925,12 +1039,18 @@
     <t>Reweighing</t>
   </si>
   <si>
+    <t>SMOTE</t>
+  </si>
+  <si>
     <t>Exp. Gradient</t>
   </si>
   <si>
     <t>Threshold Opt.</t>
   </si>
   <si>
+    <t>Reject Option</t>
+  </si>
+  <si>
     <t>RW + TO (hybrid)</t>
   </si>
   <si>
@@ -940,12 +1060,18 @@
     <t>[-0.378, -0.275]</t>
   </si>
   <si>
+    <t>[-0.372, -0.266]</t>
+  </si>
+  <si>
     <t>[-0.522, -0.409]</t>
   </si>
   <si>
     <t>[-0.565, -0.459]</t>
   </si>
   <si>
+    <t>[-0.287, -0.195]</t>
+  </si>
+  <si>
     <t>[-0.577, -0.452]</t>
   </si>
   <si>
@@ -955,12 +1081,18 @@
     <t>[-0.354, -0.258]</t>
   </si>
   <si>
+    <t>[-0.302, -0.201]</t>
+  </si>
+  <si>
     <t>[-0.330, -0.245]</t>
   </si>
   <si>
     <t>[-0.545, -0.412]</t>
   </si>
   <si>
+    <t>[-0.327, -0.232]</t>
+  </si>
+  <si>
     <t>[-0.548, -0.406]</t>
   </si>
   <si>
@@ -970,24 +1102,36 @@
     <t>[-0.052, -0.025]</t>
   </si>
   <si>
+    <t>[-0.056, -0.027]</t>
+  </si>
+  <si>
     <t>[-0.098, -0.062]</t>
   </si>
   <si>
     <t>[-0.119, -0.083]</t>
   </si>
   <si>
+    <t>[-0.037, -0.014]</t>
+  </si>
+  <si>
     <t>[-0.110, -0.072]</t>
   </si>
   <si>
     <t>[-0.020, 0.002]</t>
   </si>
   <si>
+    <t>[-0.072, -0.041]</t>
+  </si>
+  <si>
     <t>[-0.043, -0.016]</t>
   </si>
   <si>
     <t>[-0.111, -0.075]</t>
   </si>
   <si>
+    <t>[-0.034, -0.009]</t>
+  </si>
+  <si>
     <t>[-0.117, -0.081]</t>
   </si>
   <si>
@@ -1012,28 +1156,28 @@
     <t>Accuracy-driven selection</t>
   </si>
   <si>
-    <t>0.770 ± 0.003</t>
+    <t>0.744 ± 0.012</t>
   </si>
   <si>
     <t>0.756 ± 0.009</t>
   </si>
   <si>
-    <t>0.721 ± 0.000</t>
-  </si>
-  <si>
-    <t>0.642 ± 0.005</t>
+    <t>0.710 ± 0.004</t>
+  </si>
+  <si>
+    <t>0.657 ± 0.009</t>
   </si>
   <si>
     <t>0.699 ± 0.020</t>
   </si>
   <si>
-    <t>0.392 ± 0.001</t>
+    <t>0.305 ± 0.014</t>
   </si>
   <si>
     <t>0.535 ± 0.009</t>
   </si>
   <si>
-    <t>0.378 ± 0.013</t>
+    <t>0.281 ± 0.008</t>
   </si>
   <si>
     <t>0.548 ± 0.035</t>
@@ -1046,6 +1190,12 @@
   </si>
   <si>
     <t>Overall</t>
+  </si>
+  <si>
+    <t>Mean top-5 overlap (of 5)</t>
+  </si>
+  <si>
+    <t>Mean LIME local R2</t>
   </si>
 </sst>
 </file>
@@ -2283,7 +2433,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -2367,34 +2517,34 @@
         <v>191</v>
       </c>
       <c r="C3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D3" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E3" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="F3" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G3" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="H3" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="I3" t="s">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="J3" t="s">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="K3" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="L3" t="s">
-        <v>279</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2402,34 +2552,34 @@
         <v>192</v>
       </c>
       <c r="C4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D4" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E4" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="F4" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="G4" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="H4" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="I4" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="J4" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="K4" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="L4" t="s">
-        <v>280</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2437,34 +2587,34 @@
         <v>193</v>
       </c>
       <c r="C5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D5" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="E5" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="F5" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="G5" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="H5" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="I5" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="J5" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="K5" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="L5" t="s">
-        <v>281</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2472,34 +2622,34 @@
         <v>194</v>
       </c>
       <c r="C6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E6" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="F6" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="G6" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="H6" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="I6" t="s">
-        <v>258</v>
+        <v>284</v>
       </c>
       <c r="J6" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="K6" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="L6" t="s">
-        <v>282</v>
+        <v>316</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2507,253 +2657,393 @@
         <v>195</v>
       </c>
       <c r="C7" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D7" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E7" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="F7" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="G7" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="H7" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="I7" t="s">
+        <v>285</v>
+      </c>
+      <c r="J7" t="s">
+        <v>295</v>
+      </c>
+      <c r="K7" t="s">
+        <v>303</v>
+      </c>
+      <c r="L7" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="B8" t="s">
+        <v>196</v>
+      </c>
+      <c r="C8" t="s">
+        <v>203</v>
+      </c>
+      <c r="D8" t="s">
+        <v>217</v>
+      </c>
+      <c r="E8" t="s">
+        <v>231</v>
+      </c>
+      <c r="F8" t="s">
+        <v>245</v>
+      </c>
+      <c r="G8" t="s">
         <v>259</v>
       </c>
-      <c r="J7" t="s">
-        <v>266</v>
-      </c>
-      <c r="K7" t="s">
-        <v>273</v>
-      </c>
-      <c r="L7" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" t="s">
-        <v>190</v>
-      </c>
-      <c r="C8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E8" t="s">
-        <v>95</v>
-      </c>
-      <c r="F8" t="s">
-        <v>102</v>
-      </c>
-      <c r="G8" t="s">
-        <v>130</v>
-      </c>
       <c r="H8" t="s">
-        <v>138</v>
+        <v>272</v>
       </c>
       <c r="I8" t="s">
-        <v>146</v>
+        <v>286</v>
       </c>
       <c r="J8" t="s">
-        <v>146</v>
+        <v>286</v>
       </c>
       <c r="K8" t="s">
-        <v>155</v>
+        <v>304</v>
       </c>
       <c r="L8" t="s">
-        <v>162</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="B9" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C9" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D9" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E9" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="F9" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="G9" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="H9" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="I9" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="J9" t="s">
-        <v>260</v>
+        <v>296</v>
       </c>
       <c r="K9" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="L9" t="s">
-        <v>284</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>75</v>
+      </c>
       <c r="B10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C10" t="s">
-        <v>202</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>212</v>
+        <v>116</v>
       </c>
       <c r="E10" t="s">
-        <v>222</v>
+        <v>95</v>
       </c>
       <c r="F10" t="s">
-        <v>232</v>
+        <v>102</v>
       </c>
       <c r="G10" t="s">
-        <v>242</v>
+        <v>130</v>
       </c>
       <c r="H10" t="s">
-        <v>251</v>
+        <v>138</v>
       </c>
       <c r="I10" t="s">
-        <v>261</v>
+        <v>146</v>
       </c>
       <c r="J10" t="s">
-        <v>261</v>
+        <v>146</v>
       </c>
       <c r="K10" t="s">
-        <v>275</v>
+        <v>155</v>
       </c>
       <c r="L10" t="s">
-        <v>285</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C11" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D11" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E11" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="F11" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="G11" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="H11" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="I11" t="s">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="J11" t="s">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="K11" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="L11" t="s">
-        <v>286</v>
+        <v>320</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="B12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D12" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="E12" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="F12" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="G12" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="H12" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="I12" t="s">
-        <v>263</v>
+        <v>289</v>
       </c>
       <c r="J12" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="K12" t="s">
-        <v>277</v>
+        <v>307</v>
       </c>
       <c r="L12" t="s">
-        <v>287</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="B13" t="s">
+        <v>193</v>
+      </c>
+      <c r="C13" t="s">
+        <v>207</v>
+      </c>
+      <c r="D13" t="s">
+        <v>221</v>
+      </c>
+      <c r="E13" t="s">
+        <v>235</v>
+      </c>
+      <c r="F13" t="s">
+        <v>249</v>
+      </c>
+      <c r="G13" t="s">
+        <v>263</v>
+      </c>
+      <c r="H13" t="s">
+        <v>276</v>
+      </c>
+      <c r="I13" t="s">
+        <v>290</v>
+      </c>
+      <c r="J13" t="s">
+        <v>290</v>
+      </c>
+      <c r="K13" t="s">
+        <v>308</v>
+      </c>
+      <c r="L13" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="B14" t="s">
+        <v>194</v>
+      </c>
+      <c r="C14" t="s">
+        <v>208</v>
+      </c>
+      <c r="D14" t="s">
+        <v>222</v>
+      </c>
+      <c r="E14" t="s">
+        <v>236</v>
+      </c>
+      <c r="F14" t="s">
+        <v>250</v>
+      </c>
+      <c r="G14" t="s">
+        <v>264</v>
+      </c>
+      <c r="H14" t="s">
+        <v>277</v>
+      </c>
+      <c r="I14" t="s">
+        <v>291</v>
+      </c>
+      <c r="J14" t="s">
+        <v>291</v>
+      </c>
+      <c r="K14" t="s">
+        <v>309</v>
+      </c>
+      <c r="L14" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="B15" t="s">
         <v>195</v>
       </c>
-      <c r="C13" t="s">
-        <v>205</v>
-      </c>
-      <c r="D13" t="s">
-        <v>215</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="C15" t="s">
+        <v>209</v>
+      </c>
+      <c r="D15" t="s">
+        <v>223</v>
+      </c>
+      <c r="E15" t="s">
+        <v>237</v>
+      </c>
+      <c r="F15" t="s">
+        <v>251</v>
+      </c>
+      <c r="G15" t="s">
+        <v>260</v>
+      </c>
+      <c r="H15" t="s">
+        <v>278</v>
+      </c>
+      <c r="I15" t="s">
+        <v>292</v>
+      </c>
+      <c r="J15" t="s">
+        <v>297</v>
+      </c>
+      <c r="K15" t="s">
+        <v>310</v>
+      </c>
+      <c r="L15" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="B16" t="s">
+        <v>196</v>
+      </c>
+      <c r="C16" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" t="s">
+        <v>224</v>
+      </c>
+      <c r="E16" t="s">
+        <v>238</v>
+      </c>
+      <c r="F16" t="s">
+        <v>252</v>
+      </c>
+      <c r="G16" t="s">
+        <v>265</v>
+      </c>
+      <c r="H16" t="s">
+        <v>279</v>
+      </c>
+      <c r="I16" t="s">
+        <v>293</v>
+      </c>
+      <c r="J16" t="s">
+        <v>293</v>
+      </c>
+      <c r="K16" t="s">
+        <v>311</v>
+      </c>
+      <c r="L16" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12">
+      <c r="B17" t="s">
+        <v>197</v>
+      </c>
+      <c r="C17" t="s">
+        <v>211</v>
+      </c>
+      <c r="D17" t="s">
         <v>225</v>
       </c>
-      <c r="F13" t="s">
-        <v>235</v>
-      </c>
-      <c r="G13" t="s">
-        <v>244</v>
-      </c>
-      <c r="H13" t="s">
-        <v>254</v>
-      </c>
-      <c r="I13" t="s">
-        <v>264</v>
-      </c>
-      <c r="J13" t="s">
-        <v>268</v>
-      </c>
-      <c r="K13" t="s">
-        <v>278</v>
-      </c>
-      <c r="L13" t="s">
-        <v>288</v>
+      <c r="E17" t="s">
+        <v>239</v>
+      </c>
+      <c r="F17" t="s">
+        <v>253</v>
+      </c>
+      <c r="G17" t="s">
+        <v>266</v>
+      </c>
+      <c r="H17" t="s">
+        <v>280</v>
+      </c>
+      <c r="I17" t="s">
+        <v>294</v>
+      </c>
+      <c r="J17" t="s">
+        <v>298</v>
+      </c>
+      <c r="K17" t="s">
+        <v>312</v>
+      </c>
+      <c r="L17" t="s">
+        <v>326</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A10:A17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2761,7 +3051,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2843,16 +3133,16 @@
         <v>193</v>
       </c>
       <c r="C5">
-        <v>0.631</v>
+        <v>0.719</v>
       </c>
       <c r="D5">
-        <v>0.29</v>
+        <v>0.351</v>
       </c>
       <c r="E5">
-        <v>0.554</v>
+        <v>0.491</v>
       </c>
       <c r="F5">
-        <v>0.289</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2860,16 +3150,16 @@
         <v>194</v>
       </c>
       <c r="C6">
-        <v>0.5639999999999999</v>
+        <v>0.631</v>
       </c>
       <c r="D6">
-        <v>0.272</v>
+        <v>0.29</v>
       </c>
       <c r="E6">
-        <v>0.536</v>
+        <v>0.554</v>
       </c>
       <c r="F6">
-        <v>0.27</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2877,127 +3167,195 @@
         <v>195</v>
       </c>
       <c r="C7">
-        <v>0.515</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="D7">
-        <v>0.222</v>
+        <v>0.272</v>
       </c>
       <c r="E7">
-        <v>0.501</v>
+        <v>0.536</v>
       </c>
       <c r="F7">
-        <v>0.221</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>75</v>
-      </c>
       <c r="B8" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C8">
-        <v>0.848</v>
+        <v>0.789</v>
       </c>
       <c r="D8">
-        <v>0.489</v>
+        <v>0.407</v>
       </c>
       <c r="E8">
-        <v>0.317</v>
+        <v>0.496</v>
       </c>
       <c r="F8">
-        <v>0.08699999999999999</v>
+        <v>0.226</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C9">
-        <v>0.784</v>
+        <v>0.515</v>
       </c>
       <c r="D9">
-        <v>0.408</v>
+        <v>0.222</v>
       </c>
       <c r="E9">
-        <v>0.373</v>
+        <v>0.501</v>
       </c>
       <c r="F9">
-        <v>0.118</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>75</v>
+      </c>
       <c r="B10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C10">
-        <v>0.6820000000000001</v>
+        <v>0.848</v>
       </c>
       <c r="D10">
-        <v>0.264</v>
+        <v>0.489</v>
       </c>
       <c r="E10">
-        <v>0.456</v>
+        <v>0.317</v>
       </c>
       <c r="F10">
-        <v>0.203</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="B11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C11">
-        <v>0.65</v>
+        <v>0.784</v>
       </c>
       <c r="D11">
-        <v>0.232</v>
+        <v>0.408</v>
       </c>
       <c r="E11">
-        <v>0.385</v>
+        <v>0.373</v>
       </c>
       <c r="F11">
-        <v>0.14</v>
+        <v>0.118</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="B12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C12">
-        <v>0.57</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="D12">
-        <v>0.269</v>
+        <v>0.264</v>
       </c>
       <c r="E12">
-        <v>0.536</v>
+        <v>0.456</v>
       </c>
       <c r="F12">
-        <v>0.273</v>
+        <v>0.203</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="B13" t="s">
+        <v>193</v>
+      </c>
+      <c r="C13">
+        <v>0.523</v>
+      </c>
+      <c r="D13">
+        <v>0.132</v>
+      </c>
+      <c r="E13">
+        <v>0.247</v>
+      </c>
+      <c r="F13">
+        <v>0.052</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14" t="s">
+        <v>194</v>
+      </c>
+      <c r="C14">
+        <v>0.65</v>
+      </c>
+      <c r="D14">
+        <v>0.232</v>
+      </c>
+      <c r="E14">
+        <v>0.385</v>
+      </c>
+      <c r="F14">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="B15" t="s">
         <v>195</v>
       </c>
-      <c r="C13">
+      <c r="C15">
+        <v>0.57</v>
+      </c>
+      <c r="D15">
+        <v>0.269</v>
+      </c>
+      <c r="E15">
+        <v>0.536</v>
+      </c>
+      <c r="F15">
+        <v>0.273</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="B16" t="s">
+        <v>196</v>
+      </c>
+      <c r="C16">
+        <v>0.758</v>
+      </c>
+      <c r="D16">
+        <v>0.339</v>
+      </c>
+      <c r="E16">
+        <v>0.495</v>
+      </c>
+      <c r="F16">
+        <v>0.216</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" t="s">
+        <v>197</v>
+      </c>
+      <c r="C17">
         <v>0.5659999999999999</v>
       </c>
-      <c r="D13">
+      <c r="D17">
         <v>0.277</v>
       </c>
-      <c r="E13">
+      <c r="E17">
         <v>0.549</v>
       </c>
-      <c r="F13">
+      <c r="F17">
         <v>0.292</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A10:A17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3005,7 +3363,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -3016,22 +3374,22 @@
         <v>189</v>
       </c>
       <c r="D1" t="s">
-        <v>289</v>
+        <v>327</v>
       </c>
       <c r="E1" t="s">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="F1" t="s">
-        <v>291</v>
+        <v>329</v>
       </c>
       <c r="G1" t="s">
-        <v>292</v>
+        <v>330</v>
       </c>
       <c r="H1" t="s">
-        <v>293</v>
+        <v>331</v>
       </c>
       <c r="I1" t="s">
-        <v>294</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3042,13 +3400,13 @@
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>295</v>
+        <v>333</v>
       </c>
       <c r="D2">
         <v>-0.07099999999999999</v>
       </c>
       <c r="E2" t="s">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -3057,7 +3415,7 @@
         <v>-0.003</v>
       </c>
       <c r="H2" t="s">
-        <v>310</v>
+        <v>354</v>
       </c>
       <c r="I2">
         <v>0.388</v>
@@ -3071,13 +3429,13 @@
         <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>296</v>
+        <v>334</v>
       </c>
       <c r="D3">
         <v>-0.325</v>
       </c>
       <c r="E3" t="s">
-        <v>301</v>
+        <v>341</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -3086,7 +3444,7 @@
         <v>-0.039</v>
       </c>
       <c r="H3" t="s">
-        <v>311</v>
+        <v>355</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3100,22 +3458,22 @@
         <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>297</v>
+        <v>335</v>
       </c>
       <c r="D4">
-        <v>-0.466</v>
+        <v>-0.317</v>
       </c>
       <c r="E4" t="s">
-        <v>302</v>
+        <v>342</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>-0.08</v>
+        <v>-0.041</v>
       </c>
       <c r="H4" t="s">
-        <v>312</v>
+        <v>356</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3129,22 +3487,22 @@
         <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>298</v>
+        <v>336</v>
       </c>
       <c r="D5">
-        <v>-0.509</v>
+        <v>-0.466</v>
       </c>
       <c r="E5" t="s">
-        <v>303</v>
+        <v>343</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>-0.101</v>
+        <v>-0.08</v>
       </c>
       <c r="H5" t="s">
-        <v>313</v>
+        <v>357</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3158,22 +3516,22 @@
         <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>299</v>
+        <v>337</v>
       </c>
       <c r="D6">
-        <v>-0.519</v>
+        <v>-0.509</v>
       </c>
       <c r="E6" t="s">
-        <v>304</v>
+        <v>344</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>-0.091</v>
+        <v>-0.101</v>
       </c>
       <c r="H6" t="s">
-        <v>314</v>
+        <v>358</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3184,28 +3542,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>295</v>
+        <v>338</v>
       </c>
       <c r="D7">
-        <v>-0.105</v>
+        <v>-0.24</v>
       </c>
       <c r="E7" t="s">
-        <v>305</v>
+        <v>345</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>-0.008999999999999999</v>
+        <v>-0.026</v>
       </c>
       <c r="H7" t="s">
-        <v>315</v>
+        <v>359</v>
       </c>
       <c r="I7">
-        <v>0.122</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3213,25 +3571,25 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>296</v>
+        <v>339</v>
       </c>
       <c r="D8">
-        <v>-0.305</v>
+        <v>-0.519</v>
       </c>
       <c r="E8" t="s">
-        <v>306</v>
+        <v>346</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>-0.039</v>
+        <v>-0.091</v>
       </c>
       <c r="H8" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -3245,25 +3603,25 @@
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>297</v>
+        <v>333</v>
       </c>
       <c r="D9">
-        <v>-0.287</v>
+        <v>-0.105</v>
       </c>
       <c r="E9" t="s">
-        <v>307</v>
+        <v>347</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>-0.03</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H9" t="s">
-        <v>316</v>
+        <v>361</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3274,22 +3632,22 @@
         <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="D10">
-        <v>-0.488</v>
+        <v>-0.305</v>
       </c>
       <c r="E10" t="s">
-        <v>308</v>
+        <v>348</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>-0.093</v>
+        <v>-0.039</v>
       </c>
       <c r="H10" t="s">
-        <v>317</v>
+        <v>355</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -3303,24 +3661,140 @@
         <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>299</v>
+        <v>335</v>
       </c>
       <c r="D11">
+        <v>-0.25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>349</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>-0.057</v>
+      </c>
+      <c r="H11" t="s">
+        <v>362</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" t="s">
+        <v>336</v>
+      </c>
+      <c r="D12">
+        <v>-0.287</v>
+      </c>
+      <c r="E12" t="s">
+        <v>350</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>-0.03</v>
+      </c>
+      <c r="H12" t="s">
+        <v>363</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" t="s">
+        <v>337</v>
+      </c>
+      <c r="D13">
+        <v>-0.488</v>
+      </c>
+      <c r="E13" t="s">
+        <v>351</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>-0.093</v>
+      </c>
+      <c r="H13" t="s">
+        <v>364</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" t="s">
+        <v>338</v>
+      </c>
+      <c r="D14">
+        <v>-0.281</v>
+      </c>
+      <c r="E14" t="s">
+        <v>352</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>-0.022</v>
+      </c>
+      <c r="H14" t="s">
+        <v>365</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" t="s">
+        <v>339</v>
+      </c>
+      <c r="D15">
         <v>-0.487</v>
       </c>
-      <c r="E11" t="s">
-        <v>309</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
+      <c r="E15" t="s">
+        <v>353</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
         <v>-0.099</v>
       </c>
-      <c r="H11" t="s">
-        <v>318</v>
-      </c>
-      <c r="I11">
+      <c r="H15" t="s">
+        <v>366</v>
+      </c>
+      <c r="I15">
         <v>0</v>
       </c>
     </row>
@@ -3336,13 +3810,13 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" t="s">
-        <v>319</v>
+        <v>367</v>
       </c>
       <c r="C1" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="D1" t="s">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="E1" t="s">
         <v>173</v>
@@ -3351,10 +3825,10 @@
         <v>189</v>
       </c>
       <c r="G1" t="s">
-        <v>322</v>
+        <v>370</v>
       </c>
       <c r="H1" t="s">
-        <v>323</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3368,19 +3842,19 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>324</v>
+        <v>372</v>
       </c>
       <c r="E2" t="s">
         <v>75</v>
       </c>
       <c r="F2" t="s">
-        <v>295</v>
+        <v>338</v>
       </c>
       <c r="G2">
-        <v>0.724</v>
+        <v>0.72</v>
       </c>
       <c r="H2">
-        <v>0.366</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -3394,7 +3868,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>325</v>
+        <v>373</v>
       </c>
       <c r="E3" t="s">
         <v>69</v>
@@ -3420,19 +3894,19 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>324</v>
+        <v>372</v>
       </c>
       <c r="E4" t="s">
         <v>75</v>
       </c>
       <c r="F4" t="s">
-        <v>295</v>
+        <v>338</v>
       </c>
       <c r="G4">
-        <v>0.722</v>
+        <v>0.705</v>
       </c>
       <c r="H4">
-        <v>0.41</v>
+        <v>0.251</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -3446,7 +3920,7 @@
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>325</v>
+        <v>373</v>
       </c>
       <c r="E5" t="s">
         <v>75</v>
@@ -3472,19 +3946,19 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>324</v>
+        <v>372</v>
       </c>
       <c r="E6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F6" t="s">
-        <v>295</v>
+        <v>338</v>
       </c>
       <c r="G6">
-        <v>0.715</v>
+        <v>0.704</v>
       </c>
       <c r="H6">
-        <v>0.382</v>
+        <v>0.332</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -3498,7 +3972,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>325</v>
+        <v>373</v>
       </c>
       <c r="E7" t="s">
         <v>75</v>
@@ -3524,19 +3998,19 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>324</v>
+        <v>372</v>
       </c>
       <c r="E8" t="s">
         <v>75</v>
       </c>
       <c r="F8" t="s">
-        <v>295</v>
+        <v>338</v>
       </c>
       <c r="G8">
-        <v>0.726</v>
+        <v>0.708</v>
       </c>
       <c r="H8">
-        <v>0.42</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3550,7 +4024,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>325</v>
+        <v>373</v>
       </c>
       <c r="E9" t="s">
         <v>69</v>
@@ -3576,13 +4050,13 @@
         <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>324</v>
+        <v>372</v>
       </c>
       <c r="E10" t="s">
         <v>75</v>
       </c>
       <c r="F10" t="s">
-        <v>297</v>
+        <v>336</v>
       </c>
       <c r="G10">
         <v>0.709</v>
@@ -3602,7 +4076,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>325</v>
+        <v>373</v>
       </c>
       <c r="E11" t="s">
         <v>69</v>
@@ -3628,19 +4102,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>324</v>
+        <v>372</v>
       </c>
       <c r="E12" t="s">
         <v>75</v>
       </c>
       <c r="F12" t="s">
-        <v>295</v>
+        <v>338</v>
       </c>
       <c r="G12">
-        <v>0.723</v>
+        <v>0.711</v>
       </c>
       <c r="H12">
-        <v>0.392</v>
+        <v>0.244</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -3654,7 +4128,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>325</v>
+        <v>373</v>
       </c>
       <c r="E13" t="s">
         <v>69</v>
@@ -3680,19 +4154,19 @@
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>324</v>
+        <v>372</v>
       </c>
       <c r="E14" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F14" t="s">
-        <v>295</v>
+        <v>338</v>
       </c>
       <c r="G14">
-        <v>0.728</v>
+        <v>0.71</v>
       </c>
       <c r="H14">
-        <v>0.436</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -3706,7 +4180,7 @@
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>325</v>
+        <v>373</v>
       </c>
       <c r="E15" t="s">
         <v>69</v>
@@ -3732,19 +4206,19 @@
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>324</v>
+        <v>372</v>
       </c>
       <c r="E16" t="s">
         <v>75</v>
       </c>
       <c r="F16" t="s">
-        <v>295</v>
+        <v>338</v>
       </c>
       <c r="G16">
-        <v>0.715</v>
+        <v>0.713</v>
       </c>
       <c r="H16">
-        <v>0.378</v>
+        <v>0.326</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -3758,7 +4232,7 @@
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>325</v>
+        <v>373</v>
       </c>
       <c r="E17" t="s">
         <v>69</v>
@@ -3784,13 +4258,13 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>324</v>
+        <v>372</v>
       </c>
       <c r="E18" t="s">
         <v>75</v>
       </c>
       <c r="F18" t="s">
-        <v>295</v>
+        <v>333</v>
       </c>
       <c r="G18">
         <v>0.717</v>
@@ -3810,7 +4284,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>325</v>
+        <v>373</v>
       </c>
       <c r="E19" t="s">
         <v>69</v>
@@ -3836,19 +4310,19 @@
         <v>5</v>
       </c>
       <c r="D20" t="s">
-        <v>324</v>
+        <v>372</v>
       </c>
       <c r="E20" t="s">
         <v>75</v>
       </c>
       <c r="F20" t="s">
-        <v>295</v>
+        <v>338</v>
       </c>
       <c r="G20">
-        <v>0.716</v>
+        <v>0.718</v>
       </c>
       <c r="H20">
-        <v>0.384</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -3862,7 +4336,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>325</v>
+        <v>373</v>
       </c>
       <c r="E21" t="s">
         <v>69</v>
@@ -3889,7 +4363,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="B1" t="s">
         <v>63</v>
@@ -3912,48 +4386,48 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>324</v>
+        <v>372</v>
       </c>
       <c r="B2" t="s">
-        <v>326</v>
+        <v>374</v>
       </c>
       <c r="C2" t="s">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="D2" t="s">
-        <v>329</v>
+        <v>377</v>
       </c>
       <c r="E2" t="s">
-        <v>331</v>
+        <v>379</v>
       </c>
       <c r="F2" t="s">
-        <v>331</v>
+        <v>379</v>
       </c>
       <c r="G2" t="s">
-        <v>333</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>325</v>
+        <v>373</v>
       </c>
       <c r="B3" t="s">
-        <v>327</v>
+        <v>375</v>
       </c>
       <c r="C3" t="s">
         <v>116</v>
       </c>
       <c r="D3" t="s">
-        <v>330</v>
+        <v>378</v>
       </c>
       <c r="E3" t="s">
-        <v>332</v>
+        <v>380</v>
       </c>
       <c r="F3" t="s">
-        <v>332</v>
+        <v>380</v>
       </c>
       <c r="G3" t="s">
-        <v>334</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -3963,7 +4437,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -3974,7 +4448,7 @@
         <v>189</v>
       </c>
       <c r="D1" t="s">
-        <v>335</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3982,13 +4456,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>297</v>
+        <v>338</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3999,10 +4473,38 @@
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>295</v>
+        <v>336</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" t="s">
+        <v>338</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" t="s">
+        <v>333</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4012,7 +4514,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4029,7 +4531,7 @@
         <v>120</v>
       </c>
       <c r="E1" t="s">
-        <v>336</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -4082,13 +4584,13 @@
         <v>193</v>
       </c>
       <c r="C5">
-        <v>0.658</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="D5">
-        <v>0.077</v>
+        <v>0.227</v>
       </c>
       <c r="E5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4096,13 +4598,13 @@
         <v>194</v>
       </c>
       <c r="C6">
-        <v>0.642</v>
+        <v>0.658</v>
       </c>
       <c r="D6">
-        <v>0.028</v>
+        <v>0.077</v>
       </c>
       <c r="E6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4110,69 +4612,69 @@
         <v>195</v>
       </c>
       <c r="C7">
-        <v>0.644</v>
+        <v>0.642</v>
       </c>
       <c r="D7">
-        <v>0.016</v>
+        <v>0.028</v>
       </c>
       <c r="E7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>75</v>
-      </c>
       <c r="B8" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C8">
-        <v>0.734</v>
+        <v>0.707</v>
       </c>
       <c r="D8">
-        <v>0.531</v>
+        <v>0.293</v>
       </c>
       <c r="E8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C9">
-        <v>0.722</v>
+        <v>0.644</v>
       </c>
       <c r="D9">
-        <v>0.411</v>
+        <v>0.016</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>75</v>
+      </c>
       <c r="B10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C10">
-        <v>0.6929999999999999</v>
+        <v>0.734</v>
       </c>
       <c r="D10">
-        <v>0.226</v>
+        <v>0.531</v>
       </c>
       <c r="E10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="B11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C11">
-        <v>0.698</v>
+        <v>0.722</v>
       </c>
       <c r="D11">
-        <v>0.265</v>
+        <v>0.411</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
@@ -4180,13 +4682,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="B12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C12">
-        <v>0.644</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="D12">
-        <v>0.035</v>
+        <v>0.226</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -4194,22 +4696,78 @@
     </row>
     <row r="13" spans="1:5">
       <c r="B13" t="s">
+        <v>193</v>
+      </c>
+      <c r="C13">
+        <v>0.678</v>
+      </c>
+      <c r="D13">
+        <v>0.276</v>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="B14" t="s">
+        <v>194</v>
+      </c>
+      <c r="C14">
+        <v>0.698</v>
+      </c>
+      <c r="D14">
+        <v>0.265</v>
+      </c>
+      <c r="E14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" t="s">
         <v>195</v>
       </c>
-      <c r="C13">
+      <c r="C15">
+        <v>0.644</v>
+      </c>
+      <c r="D15">
+        <v>0.035</v>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="B16" t="s">
+        <v>196</v>
+      </c>
+      <c r="C16">
+        <v>0.709</v>
+      </c>
+      <c r="D16">
+        <v>0.263</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" t="s">
+        <v>197</v>
+      </c>
+      <c r="C17">
         <v>0.636</v>
       </c>
-      <c r="D13">
+      <c r="D17">
         <v>0.025</v>
       </c>
-      <c r="E13" t="b">
+      <c r="E17" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A10:A17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4217,377 +4775,256 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:4">
       <c r="B1" t="s">
-        <v>173</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I1" t="s">
-        <v>120</v>
-      </c>
-      <c r="J1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" t="s">
-        <v>190</v>
+        <v>385</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2">
+        <v>0.5386999845504761</v>
+      </c>
+      <c r="C2">
+        <v>0.4790999889373779</v>
       </c>
       <c r="D2">
-        <v>0.784</v>
-      </c>
-      <c r="E2">
-        <v>0.749</v>
-      </c>
-      <c r="F2">
-        <v>0.696</v>
-      </c>
-      <c r="G2">
-        <v>0.8070000000000001</v>
-      </c>
-      <c r="H2">
-        <v>0.475</v>
-      </c>
-      <c r="I2">
-        <v>0.508</v>
-      </c>
-      <c r="J2">
-        <v>0.872</v>
-      </c>
-      <c r="K2">
-        <v>0.396</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" t="s">
-        <v>296</v>
+        <v>0.5005999803543091</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3">
+        <v>0.5501000285148621</v>
+      </c>
+      <c r="C3">
+        <v>0.3258000016212463</v>
       </c>
       <c r="D3">
-        <v>0.742</v>
-      </c>
-      <c r="E3">
-        <v>0.705</v>
-      </c>
-      <c r="F3">
-        <v>0.65</v>
-      </c>
-      <c r="G3">
-        <v>0.757</v>
-      </c>
-      <c r="H3">
-        <v>0.173</v>
-      </c>
-      <c r="I3">
-        <v>0.173</v>
-      </c>
-      <c r="J3">
-        <v>0.714</v>
-      </c>
-      <c r="K3">
-        <v>0.541</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" t="s">
-        <v>297</v>
+        <v>0.4066999852657318</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4">
+        <v>0.268200010061264</v>
+      </c>
+      <c r="C4">
+        <v>0.223800003528595</v>
       </c>
       <c r="D4">
-        <v>0.6820000000000001</v>
-      </c>
-      <c r="E4">
-        <v>0.656</v>
-      </c>
-      <c r="F4">
-        <v>0.618</v>
-      </c>
-      <c r="G4">
-        <v>0.659</v>
-      </c>
-      <c r="H4">
-        <v>0.017</v>
-      </c>
-      <c r="I4">
-        <v>0.066</v>
-      </c>
-      <c r="J4">
-        <v>0.624</v>
-      </c>
-      <c r="K4">
-        <v>0.607</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" t="s">
-        <v>298</v>
+        <v>0.2398000061511993</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5">
+        <v>0.2693000137805939</v>
+      </c>
+      <c r="C5">
+        <v>0.2179999947547913</v>
       </c>
       <c r="D5">
-        <v>0.673</v>
-      </c>
-      <c r="E5">
-        <v>0.644</v>
-      </c>
-      <c r="F5">
-        <v>0.601</v>
-      </c>
-      <c r="H5">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="I5">
-        <v>0.021</v>
-      </c>
-      <c r="J5">
-        <v>0.598</v>
-      </c>
-      <c r="K5">
-        <v>0.607</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" t="s">
-        <v>299</v>
+        <v>0.2364999949932098</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6">
+        <v>0.2093999981880188</v>
+      </c>
+      <c r="C6">
+        <v>0.1606000065803528</v>
       </c>
       <c r="D6">
-        <v>0.712</v>
-      </c>
-      <c r="E6">
-        <v>0.657</v>
-      </c>
-      <c r="F6">
-        <v>0.576</v>
-      </c>
-      <c r="H6">
-        <v>0.034</v>
-      </c>
-      <c r="I6">
-        <v>0.034</v>
-      </c>
-      <c r="J6">
-        <v>0.5629999999999999</v>
-      </c>
-      <c r="K6">
-        <v>0.597</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" t="s">
-        <v>190</v>
+        <v>0.1782000064849854</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7">
+        <v>0.1842000037431717</v>
+      </c>
+      <c r="C7">
+        <v>0.1621000021696091</v>
       </c>
       <c r="D7">
-        <v>0.791</v>
-      </c>
-      <c r="E7">
-        <v>0.74</v>
-      </c>
-      <c r="F7">
-        <v>0.666</v>
-      </c>
-      <c r="G7">
-        <v>0.8139999999999999</v>
-      </c>
-      <c r="H7">
-        <v>0.453</v>
-      </c>
-      <c r="I7">
-        <v>0.453</v>
-      </c>
-      <c r="J7">
-        <v>0.833</v>
-      </c>
-      <c r="K7">
-        <v>0.381</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" t="s">
-        <v>296</v>
+        <v>0.1701000034809113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8">
+        <v>0.1221000030636787</v>
+      </c>
+      <c r="C8">
+        <v>0.1264999955892563</v>
       </c>
       <c r="D8">
-        <v>0.744</v>
-      </c>
-      <c r="E8">
-        <v>0.696</v>
-      </c>
-      <c r="F8">
-        <v>0.626</v>
-      </c>
-      <c r="G8">
-        <v>0.759</v>
-      </c>
-      <c r="H8">
-        <v>0.109</v>
-      </c>
-      <c r="I8">
-        <v>0.109</v>
-      </c>
-      <c r="J8">
-        <v>0.666</v>
-      </c>
-      <c r="K8">
-        <v>0.5570000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" t="s">
-        <v>297</v>
+        <v>0.1248999983072281</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9">
+        <v>0.1242000013589859</v>
+      </c>
+      <c r="C9">
+        <v>0.1247999966144562</v>
       </c>
       <c r="D9">
-        <v>0.791</v>
-      </c>
-      <c r="E9">
-        <v>0.698</v>
-      </c>
-      <c r="F9">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="G9">
-        <v>0.732</v>
-      </c>
-      <c r="H9">
-        <v>0.131</v>
-      </c>
-      <c r="I9">
-        <v>0.131</v>
-      </c>
-      <c r="J9">
-        <v>0.609</v>
-      </c>
-      <c r="K9">
-        <v>0.478</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" t="s">
-        <v>298</v>
+        <v>0.124600000679493</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10">
+        <v>0.08990000188350677</v>
+      </c>
+      <c r="C10">
+        <v>0.1396999955177307</v>
       </c>
       <c r="D10">
-        <v>0.696</v>
-      </c>
-      <c r="E10">
-        <v>0.663</v>
-      </c>
-      <c r="F10">
-        <v>0.614</v>
-      </c>
-      <c r="H10">
-        <v>0.073</v>
-      </c>
-      <c r="I10">
-        <v>0.073</v>
-      </c>
-      <c r="J10">
-        <v>0.587</v>
-      </c>
-      <c r="K10">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>299</v>
+        <v>0.1216999962925911</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11">
+        <v>0.1092000007629395</v>
+      </c>
+      <c r="C11">
+        <v>0.1140000000596046</v>
       </c>
       <c r="D11">
-        <v>0.668</v>
-      </c>
-      <c r="E11">
-        <v>0.653</v>
-      </c>
-      <c r="F11">
-        <v>0.63</v>
-      </c>
-      <c r="H11">
-        <v>0.092</v>
-      </c>
-      <c r="I11">
-        <v>0.092</v>
-      </c>
-      <c r="J11">
-        <v>0.596</v>
-      </c>
-      <c r="K11">
-        <v>0.6889999999999999</v>
+        <v>0.1123000010848045</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12">
+        <v>0.09529999643564224</v>
+      </c>
+      <c r="C12">
+        <v>0.08820000290870667</v>
+      </c>
+      <c r="D12">
+        <v>0.09070000052452087</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13">
+        <v>0.08820000290870667</v>
+      </c>
+      <c r="C13">
+        <v>0.09149999916553497</v>
+      </c>
+      <c r="D13">
+        <v>0.09030000120401382</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14">
+        <v>0.09000000357627869</v>
+      </c>
+      <c r="C14">
+        <v>0.06639999896287918</v>
+      </c>
+      <c r="D14">
+        <v>0.07490000128746033</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15">
+        <v>0.06710000336170197</v>
+      </c>
+      <c r="C15">
+        <v>0.06530000269412994</v>
+      </c>
+      <c r="D15">
+        <v>0.06599999964237213</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16">
+        <v>0.05270000174641609</v>
+      </c>
+      <c r="C16">
+        <v>0.05689999833703041</v>
+      </c>
+      <c r="D16">
+        <v>0.05539999902248383</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17">
+        <v>0.02820000052452087</v>
+      </c>
+      <c r="C17">
+        <v>0.02879999950528145</v>
+      </c>
+      <c r="D17">
+        <v>0.02859999984502792</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4597,256 +5034,63 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>21</v>
+        <v>386</v>
       </c>
       <c r="D1" t="s">
-        <v>337</v>
+        <v>387</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="B2">
-        <v>0.5386999845504761</v>
+        <v>25</v>
       </c>
       <c r="C2">
-        <v>0.4790999889373779</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>0.5005999803543091</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="B3">
-        <v>0.5501000285148621</v>
+        <v>25</v>
       </c>
       <c r="C3">
-        <v>0.3258000016212463</v>
+        <v>3.24</v>
       </c>
       <c r="D3">
-        <v>0.4066999852657318</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="B4">
-        <v>0.268200010061264</v>
+        <v>50</v>
       </c>
       <c r="C4">
-        <v>0.223800003528595</v>
+        <v>3.12</v>
       </c>
       <c r="D4">
-        <v>0.2398000061511993</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5">
-        <v>0.2693000137805939</v>
-      </c>
-      <c r="C5">
-        <v>0.2179999947547913</v>
-      </c>
-      <c r="D5">
-        <v>0.2364999949932098</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6">
-        <v>0.2093999981880188</v>
-      </c>
-      <c r="C6">
-        <v>0.1606000065803528</v>
-      </c>
-      <c r="D6">
-        <v>0.1782000064849854</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7">
-        <v>0.1842000037431717</v>
-      </c>
-      <c r="C7">
-        <v>0.1621000021696091</v>
-      </c>
-      <c r="D7">
-        <v>0.1701000034809113</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8">
-        <v>0.1221000030636787</v>
-      </c>
-      <c r="C8">
-        <v>0.1264999955892563</v>
-      </c>
-      <c r="D8">
-        <v>0.1248999983072281</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9">
-        <v>0.1242000013589859</v>
-      </c>
-      <c r="C9">
-        <v>0.1247999966144562</v>
-      </c>
-      <c r="D9">
-        <v>0.124600000679493</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>60</v>
-      </c>
-      <c r="B10">
-        <v>0.08990000188350677</v>
-      </c>
-      <c r="C10">
-        <v>0.1396999955177307</v>
-      </c>
-      <c r="D10">
-        <v>0.1216999962925911</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11">
-        <v>0.1092000007629395</v>
-      </c>
-      <c r="C11">
-        <v>0.1140000000596046</v>
-      </c>
-      <c r="D11">
-        <v>0.1123000010848045</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12">
-        <v>0.09529999643564224</v>
-      </c>
-      <c r="C12">
-        <v>0.08820000290870667</v>
-      </c>
-      <c r="D12">
-        <v>0.09070000052452087</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13">
-        <v>0.08820000290870667</v>
-      </c>
-      <c r="C13">
-        <v>0.09149999916553497</v>
-      </c>
-      <c r="D13">
-        <v>0.09030000120401382</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14">
-        <v>0.09000000357627869</v>
-      </c>
-      <c r="C14">
-        <v>0.06639999896287918</v>
-      </c>
-      <c r="D14">
-        <v>0.07490000128746033</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15">
-        <v>0.06710000336170197</v>
-      </c>
-      <c r="C15">
-        <v>0.06530000269412994</v>
-      </c>
-      <c r="D15">
-        <v>0.06599999964237213</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>62</v>
-      </c>
-      <c r="B16">
-        <v>0.05270000174641609</v>
-      </c>
-      <c r="C16">
-        <v>0.05689999833703041</v>
-      </c>
-      <c r="D16">
-        <v>0.05539999902248383</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17">
-        <v>0.02820000052452087</v>
-      </c>
-      <c r="C17">
-        <v>0.02879999950528145</v>
-      </c>
-      <c r="D17">
-        <v>0.02859999984502792</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
